--- a/CourseDetails.xlsx
+++ b/CourseDetails.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Course Name</t>
   </si>
@@ -29,16 +29,13 @@
     <t>1 - 4 Weeks</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Meta Full Stack Developer: Front-End &amp; Back-End from Scratch</t>
   </si>
   <si>
     <t>3 - 6 Months</t>
-  </si>
-  <si>
-    <t>4.7</t>
   </si>
 </sst>
 </file>
@@ -121,7 +118,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
